--- a/Employee_Reports_wi52/Kishanraj Pulenthiran Q0524.xlsx
+++ b/Employee_Reports_wi52/Kishanraj Pulenthiran Q0524.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1479,20 +1479,20 @@
       <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>315</v>
+        <v>727</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
